--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486663_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486663_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.295</v>
+        <v>6.8296</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0217</v>
+        <v>4.7163</v>
       </c>
       <c r="F2" t="n">
-        <v>6.2733</v>
+        <v>2.1133</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1277</v>
+        <v>3.9428</v>
       </c>
       <c r="H2" t="n">
-        <v>2.69</v>
+        <v>1.7726</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4378</v>
+        <v>2.1702</v>
       </c>
       <c r="J2" t="n">
-        <v>2.164</v>
+        <v>4.3852</v>
       </c>
       <c r="K2" t="n">
-        <v>0.898</v>
+        <v>1.2903</v>
       </c>
       <c r="L2" t="n">
-        <v>1.266</v>
+        <v>3.0949</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9637</v>
+        <v>-0.4424</v>
       </c>
       <c r="N2" t="n">
-        <v>1.792</v>
+        <v>0.4822</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1717</v>
+        <v>-0.9247</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0892</v>
+        <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1093</v>
+        <v>0.1378</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.111</v>
+        <v>-0.1936</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2203</v>
+        <v>0.3313</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8995</v>
+        <v>2.1698</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8995</v>
+        <v>2.4554</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7484</v>
+        <v>6.4066</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8337</v>
+        <v>1.0769</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9146</v>
+        <v>5.3297</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9428</v>
+        <v>4.1277</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7726</v>
+        <v>2.69</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1702</v>
+        <v>1.4378</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3852</v>
+        <v>2.164</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2903</v>
+        <v>0.898</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0949</v>
+        <v>1.266</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4424</v>
+        <v>1.9637</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4822</v>
+        <v>1.792</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9247</v>
+        <v>0.1717</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>2.51</v>
+        <v>3.0892</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9434</v>
+        <v>0.2209</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1327</v>
+        <v>0.2767</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1698</v>
+        <v>0.8995</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4554</v>
+        <v>0.8995</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3036</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5736</v>
+        <v>3.1459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.73</v>
+        <v>0.8541</v>
       </c>
       <c r="G4" t="n">
         <v>0.163</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4966</v>
+        <v>0.1999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8554</v>
+        <v>-0.2831</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3588</v>
+        <v>0.483</v>
       </c>
       <c r="V4" t="n">
         <v>1.5133</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>J. LUJAN MARCOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1401</v>
+        <v>1.5786</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1053</v>
+        <v>0.2616</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0349</v>
+        <v>1.3169</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8151</v>
+        <v>-0.9248</v>
       </c>
       <c r="H5" t="n">
-        <v>1.221</v>
+        <v>-0.2827</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.0361</v>
+        <v>-0.642</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6967</v>
+        <v>-1.2762</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0886</v>
+        <v>-0.6274</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6081</v>
+        <v>-0.6488</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1184</v>
+        <v>0.3514</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3096</v>
+        <v>0.3447</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.428</v>
+        <v>0.0068</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>1.125</v>
+        <v>0.3103</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9025</v>
+        <v>0.3101</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7775</v>
+        <v>0.0001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8995</v>
+        <v>1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8995</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LUJAN MARCOS</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.682</v>
+        <v>1.1047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3651</v>
+        <v>0.8712</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3169</v>
+        <v>0.2335</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9248</v>
+        <v>-1.8151</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2827</v>
+        <v>1.221</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.642</v>
+        <v>-3.0361</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2762</v>
+        <v>-0.6967</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6274</v>
+        <v>-0.0886</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6488</v>
+        <v>-0.6081</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3514</v>
+        <v>-1.1184</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3447</v>
+        <v>1.3096</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0068</v>
+        <v>-2.428</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4137</v>
+        <v>0.0895</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4136</v>
+        <v>0.6684</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001</v>
+        <v>-0.5789</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2277</v>
+        <v>0.8995</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2277</v>
+        <v>0.8995</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1318</v>
+        <v>0.7911</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4356</v>
+        <v>-1.1736</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5674</v>
+        <v>1.9647</v>
       </c>
       <c r="G7" t="n">
         <v>1.0805</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9142</v>
+        <v>-1.2548</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7174</v>
+        <v>-0.4553</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1968</v>
+        <v>-0.7995</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5409</v>
+        <v>-0.7711</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.641</v>
+        <v>-0.8961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1002</v>
+        <v>0.125</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8277</v>
@@ -1078,13 +1078,13 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7558</v>
+        <v>-0.986</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1377</v>
+        <v>-0.1174</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8934</v>
+        <v>-0.8686</v>
       </c>
       <c r="V8" t="n">
         <v>0.6565</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9492</v>
+        <v>-2.0457</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.0528</v>
+        <v>-3.4098</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1035</v>
+        <v>1.3642</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.6283</v>
+        <v>-4.1762</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.8884</v>
+        <v>0.2004</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7399</v>
+        <v>-4.3767</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.4411</v>
+        <v>-1.8301</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.7155</v>
+        <v>-0.0059</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7256</v>
+        <v>-1.8243</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1872</v>
+        <v>-2.3461</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.2063</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0143</v>
+        <v>-2.5524</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6685</v>
+        <v>1.1585</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6685</v>
+        <v>3.0892</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9527</v>
+        <v>0.9721</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1027</v>
+        <v>0.3511</v>
       </c>
       <c r="U9" t="n">
-        <v>0.85</v>
+        <v>0.621</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3284</v>
+        <v>-2.2852</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5684</v>
+        <v>-2.2154</v>
       </c>
       <c r="F10" t="n">
-        <v>1.24</v>
+        <v>-0.0699</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1762</v>
+        <v>0.025</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2004</v>
+        <v>1.3927</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3767</v>
+        <v>-1.3677</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8301</v>
+        <v>-0.1395</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0059</v>
+        <v>0.4279</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8243</v>
+        <v>-0.5674</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3461</v>
+        <v>0.1645</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2063</v>
+        <v>0.9648</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5524</v>
+        <v>-0.8003</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0892</v>
+        <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6893</v>
+        <v>-0.6964</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1925</v>
+        <v>-0.1451</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4968</v>
+        <v>-0.5513</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9072</v>
+        <v>-2.4816</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7877</v>
+        <v>-4.4113</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1195</v>
+        <v>1.9297</v>
       </c>
       <c r="G11" t="n">
-        <v>0.025</v>
+        <v>-6.6283</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3927</v>
+        <v>-3.8884</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3677</v>
+        <v>-2.7399</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1395</v>
+        <v>-5.4411</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4279</v>
+        <v>-4.7155</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5674</v>
+        <v>-0.7256</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1645</v>
+        <v>-1.1872</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9648</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8003</v>
+        <v>-2.0143</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3862</v>
+        <v>3.6685</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5446</v>
+        <v>3.6685</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3183</v>
+        <v>1.4203</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7174</v>
+        <v>0.7442</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.601</v>
+        <v>0.6762</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-0.9421</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2277</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.5752</v>
+        <v>13.127</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.586100000000001</v>
+        <v>-2.034299999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1613</v>
+        <v>15.1612</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0331</v>
+        <v>-5.033100000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.484400000000001</v>
+        <v>4.4844</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.517399999999999</v>
+        <v>-9.5174</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6434</v>
+        <v>-3.643399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.750899999999999</v>
+        <v>-2.7509</v>
       </c>
       <c r="L12" t="n">
         <v>-0.8925</v>
@@ -1375,7 +1375,7 @@
         <v>-1.3898</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2353</v>
+        <v>7.235300000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-8.625</v>
@@ -1390,19 +1390,19 @@
         <v>20.2732</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1382999999999999</v>
+        <v>0.4136</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2716999999999997</v>
+        <v>0.8234999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4099999999999999</v>
+        <v>-0.4100000000000003</v>
       </c>
       <c r="V12" t="n">
         <v>5.1965</v>
       </c>
       <c r="W12" t="n">
-        <v>8.508699999999999</v>
+        <v>8.508700000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-3.3122</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6561</v>
+        <v>2.0008</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2052</v>
+        <v>0.0017</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8612</v>
+        <v>1.9991</v>
       </c>
       <c r="G13" t="n">
         <v>0.929</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5239</v>
+        <v>-0.1792</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4416</v>
+        <v>-0.2347</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0824</v>
+        <v>0.0555</v>
       </c>
       <c r="V13" t="n">
         <v>0.2856</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6215</v>
+        <v>1.6352</v>
       </c>
       <c r="E14" t="n">
         <v>2.4914</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8699</v>
+        <v>-0.8562</v>
       </c>
       <c r="G14" t="n">
         <v>4.2627</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2204</v>
+        <v>-0.2067</v>
       </c>
       <c r="T14" t="n">
         <v>-0.4691</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2487</v>
+        <v>0.2624</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8415</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1876</v>
+        <v>0.2635</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0854</v>
+        <v>-0.2249</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1022</v>
+        <v>0.4885</v>
       </c>
       <c r="G15" t="n">
         <v>5.4765</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4965</v>
+        <v>-0.4206</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1659</v>
+        <v>-0.4762</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3306</v>
+        <v>0.0556</v>
       </c>
       <c r="V15" t="n">
         <v>0.6138</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0987</v>
+        <v>-0.1864</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5223</v>
+        <v>-1.1102</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4237</v>
+        <v>0.9238</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0626</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3593</v>
+        <v>0.4342</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4219</v>
+        <v>0.1379</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.398</v>
+        <v>0.0207</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5653</v>
+        <v>0.0207</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1673</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4606</v>
+        <v>0.5514</v>
       </c>
       <c r="N16" t="n">
-        <v>0.206</v>
+        <v>0.4135</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2546</v>
+        <v>0.1379</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5446</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.51</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9546</v>
+        <v>-0.1793</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3857</v>
+        <v>-0.1655</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5689</v>
+        <v>-0.0137</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2609</v>
+        <v>-0.4118</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1102</v>
+        <v>-2.6257</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8494</v>
+        <v>2.2139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5721000000000001</v>
+        <v>1.0626</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4342</v>
+        <v>-0.3593</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1379</v>
+        <v>1.4219</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0207</v>
+        <v>-0.398</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>-0.5653</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1673</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5514</v>
+        <v>1.4606</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4135</v>
+        <v>0.206</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1379</v>
+        <v>1.2546</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-2.51</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2538</v>
+        <v>0.6414</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1655</v>
+        <v>0.2823</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0882</v>
+        <v>0.3592</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2863</v>
+        <v>-1.3637</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.429</v>
+        <v>-1.2221</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1426</v>
+        <v>-0.1416</v>
       </c>
       <c r="G18" t="n">
         <v>1.701</v>
@@ -1858,13 +1858,13 @@
         <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1052</v>
+        <v>0.0278</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3587</v>
+        <v>-0.1519</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4639</v>
+        <v>0.1797</v>
       </c>
       <c r="V18" t="n">
         <v>-2.1271</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3504</v>
+        <v>-2.2923</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6498</v>
+        <v>-1.0635</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7006</v>
+        <v>-1.2288</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6234</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2037</v>
+        <v>0.2618</v>
       </c>
       <c r="T19" t="n">
-        <v>1.075</v>
+        <v>0.6614</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8713</v>
+        <v>-0.3995</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1687</v>
+        <v>-3.4831</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2065</v>
+        <v>-3.6202</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0378</v>
+        <v>0.1372</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9518</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9762</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2682</v>
+        <v>0.8546</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.292</v>
+        <v>-0.1927</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6138</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4369</v>
+        <v>-3.9253</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7252</v>
+        <v>-4.476</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7116</v>
+        <v>0.5507</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0398</v>
+        <v>-3.3558</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9239000000000001</v>
+        <v>-3.661</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9637</v>
+        <v>0.3051</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1348</v>
+        <v>-3.244</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5802</v>
+        <v>-3.9358</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.7149</v>
+        <v>0.6918</v>
       </c>
       <c r="M21" t="n">
-        <v>0.095</v>
+        <v>-0.1118</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3437</v>
+        <v>0.2749</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2487</v>
+        <v>-0.3866</v>
       </c>
       <c r="P21" t="n">
         <v>-0.9654</v>
@@ -2092,28 +2092,28 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.204</v>
+        <v>0.1102</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3314</v>
+        <v>0.0271</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1275</v>
+        <v>0.0832</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W21" t="n">
         <v>0.2856</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4384</v>
+        <v>-4.1225</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8897</v>
+        <v>-3.3115</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4513</v>
+        <v>-0.8109</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3558</v>
+        <v>-2.0398</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.661</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3051</v>
+        <v>-2.9637</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.244</v>
+        <v>-2.1348</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.9358</v>
+        <v>0.5802</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6918</v>
+        <v>-2.7149</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1118</v>
+        <v>0.095</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2749</v>
+        <v>0.3437</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3866</v>
+        <v>-0.2487</v>
       </c>
       <c r="P22" t="n">
         <v>-0.9654</v>
@@ -2170,22 +2170,22 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4028</v>
+        <v>0.1104</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3866</v>
+        <v>0.0822</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0161</v>
+        <v>0.0281</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W22" t="n">
         <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="23">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.5751</v>
+        <v>-11.8856</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.1611</v>
+        <v>-15.161</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5861</v>
+        <v>3.275700000000001</v>
       </c>
       <c r="G23" t="n">
         <v>5.033099999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.4844</v>
+        <v>-4.484400000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>9.517300000000001</v>
+        <v>9.517299999999999</v>
       </c>
       <c r="J23" t="n">
         <v>1.389699999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.2351</v>
+        <v>-7.235100000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.6249</v>
+        <v>8.624900000000002</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6434</v>
+        <v>3.643400000000001</v>
       </c>
       <c r="N23" t="n">
         <v>2.7508</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8924999999999998</v>
+        <v>0.8925</v>
       </c>
       <c r="P23" t="n">
         <v>-12.55</v>
@@ -2248,13 +2248,13 @@
         <v>7.723100000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1382999999999999</v>
+        <v>0.8275999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4101</v>
+        <v>0.4102000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2716000000000001</v>
+        <v>0.4178</v>
       </c>
       <c r="V23" t="n">
         <v>-5.1963</v>
@@ -2263,7 +2263,7 @@
         <v>3.3122</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.5084</v>
+        <v>-8.508399999999998</v>
       </c>
     </row>
   </sheetData>
